--- a/data/interim/itu_fixed_broad_price_processed.xlsx
+++ b/data/interim/itu_fixed_broad_price_processed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>fixed_broad_price_usd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>fixed_broad_price_gni_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>fixed_broad_price_ppp</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>series_code</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>series_units</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>data_source</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
@@ -495,7 +483,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +522,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -573,7 +561,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -612,7 +600,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -651,7 +639,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -690,7 +678,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -729,7 +717,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -768,7 +756,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -807,7 +795,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -846,7 +834,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -885,7 +873,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -924,7 +912,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -963,7 +951,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1002,7 +990,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1041,7 +1029,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1080,7 +1068,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1119,7 +1107,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,7 +1146,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1197,7 +1185,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1236,7 +1224,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1275,7 +1263,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1314,7 +1302,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1353,7 +1341,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1392,7 +1380,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1431,7 +1419,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1470,7 +1458,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1509,7 +1497,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1548,7 +1536,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1587,7 +1575,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1626,7 +1614,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1665,7 +1653,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1704,7 +1692,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1743,7 +1731,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1782,7 +1770,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1819,7 +1807,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1856,7 +1844,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1893,7 +1881,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1932,7 +1920,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1971,7 +1959,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2010,7 +1998,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2049,7 +2037,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2088,7 +2076,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2127,7 +2115,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2166,7 +2154,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2205,7 +2193,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2244,7 +2232,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2283,7 +2271,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2322,7 +2310,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2361,7 +2349,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2400,7 +2388,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2439,7 +2427,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2478,7 +2466,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2517,7 +2505,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2556,7 +2544,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2595,7 +2583,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2634,7 +2622,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2673,7 +2661,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2712,7 +2700,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2751,7 +2739,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2790,7 +2778,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2829,7 +2817,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2868,7 +2856,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2907,7 +2895,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2946,7 +2934,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2985,7 +2973,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3024,7 +3012,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3063,7 +3051,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3102,7 +3090,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3141,7 +3129,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3180,7 +3168,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3219,7 +3207,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3258,7 +3246,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3297,7 +3285,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3336,7 +3324,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3375,7 +3363,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3414,7 +3402,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3453,7 +3441,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3492,7 +3480,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3531,7 +3519,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3568,7 +3556,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3605,7 +3593,7 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3642,7 +3630,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3681,7 +3669,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3720,7 +3708,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3759,7 +3747,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3798,7 +3786,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3837,7 +3825,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3876,7 +3864,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3915,7 +3903,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3954,7 +3942,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3993,7 +3981,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4032,7 +4020,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4071,7 +4059,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4110,7 +4098,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4149,7 +4137,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4188,7 +4176,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4227,7 +4215,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4266,7 +4254,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4305,7 +4293,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4344,7 +4332,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4383,7 +4371,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4422,7 +4410,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4461,7 +4449,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4500,7 +4488,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4539,7 +4527,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4578,7 +4566,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4617,7 +4605,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4656,7 +4644,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4695,7 +4683,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4734,7 +4722,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4773,7 +4761,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4812,7 +4800,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4851,7 +4839,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4890,7 +4878,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4929,7 +4917,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4968,7 +4956,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5007,7 +4995,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5046,7 +5034,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5085,7 +5073,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5124,7 +5112,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5163,7 +5151,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5202,7 +5190,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5241,7 +5229,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5280,7 +5268,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5319,7 +5307,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5358,7 +5346,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5397,7 +5385,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5436,7 +5424,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5475,7 +5463,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5514,7 +5502,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5553,7 +5541,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5592,7 +5580,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5631,7 +5619,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5670,7 +5658,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5709,7 +5697,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5748,7 +5736,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5787,7 +5775,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5826,7 +5814,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5865,7 +5853,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5904,7 +5892,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5943,7 +5931,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5982,7 +5970,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6021,7 +6009,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6060,7 +6048,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6099,7 +6087,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6138,7 +6126,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6177,7 +6165,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6216,7 +6204,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6255,7 +6243,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6294,7 +6282,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6333,7 +6321,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6372,7 +6360,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6411,7 +6399,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6450,7 +6438,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6489,7 +6477,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6528,7 +6516,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6567,7 +6555,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6606,7 +6594,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6645,7 +6633,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6684,7 +6672,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6723,7 +6711,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6762,7 +6750,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6801,7 +6789,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6840,7 +6828,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6879,7 +6867,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6918,7 +6906,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -6957,7 +6945,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6996,7 +6984,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7035,7 +7023,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7074,7 +7062,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7113,7 +7101,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7152,7 +7140,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7191,7 +7179,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7230,7 +7218,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7269,7 +7257,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7308,7 +7296,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7347,7 +7335,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7386,7 +7374,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7425,7 +7413,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7464,7 +7452,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7503,7 +7491,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -7542,7 +7530,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7581,7 +7569,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7620,7 +7608,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7659,7 +7647,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7698,7 +7686,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7737,7 +7725,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7776,7 +7764,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7815,7 +7803,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7854,7 +7842,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7893,7 +7881,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -7932,7 +7920,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7971,7 +7959,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8010,7 +7998,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8049,7 +8037,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -8088,7 +8076,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8127,7 +8115,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -8166,7 +8154,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8205,7 +8193,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -8244,7 +8232,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -8283,7 +8271,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8322,7 +8310,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8361,7 +8349,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -8400,7 +8388,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -8439,7 +8427,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -8478,7 +8466,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -8517,7 +8505,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -8556,7 +8544,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -8595,7 +8583,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -8634,7 +8622,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -8673,7 +8661,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -8712,7 +8700,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8751,7 +8739,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -8790,7 +8778,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -8829,7 +8817,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -8868,7 +8856,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -8907,7 +8895,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -8946,7 +8934,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -8983,7 +8971,7 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -9020,7 +9008,7 @@
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9059,7 +9047,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -9098,7 +9086,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -9137,7 +9125,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -9176,7 +9164,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -9215,7 +9203,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -9254,7 +9242,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -9293,7 +9281,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -9332,7 +9320,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -9371,7 +9359,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -9410,7 +9398,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -9449,7 +9437,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -9488,7 +9476,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -9527,7 +9515,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -9566,7 +9554,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -9605,7 +9593,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -9644,7 +9632,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -9683,7 +9671,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -9722,7 +9710,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -9761,7 +9749,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -9800,7 +9788,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -9839,7 +9827,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -9878,7 +9866,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -9917,7 +9905,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -9956,7 +9944,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -9995,7 +9983,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -10034,7 +10022,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -10073,7 +10061,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -10112,7 +10100,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -10151,7 +10139,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -10190,7 +10178,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -10229,7 +10217,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -10268,7 +10256,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -10307,7 +10295,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -10346,7 +10334,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -10385,7 +10373,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -10424,7 +10412,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -10463,7 +10451,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -10502,7 +10490,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -10541,7 +10529,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -10580,7 +10568,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -10619,7 +10607,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -10658,7 +10646,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -10697,7 +10685,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -10736,7 +10724,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -10775,7 +10763,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -10814,7 +10802,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -10853,7 +10841,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -10892,7 +10880,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -10931,7 +10919,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -10970,7 +10958,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -11009,7 +10997,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -11048,7 +11036,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -11087,7 +11075,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -11126,7 +11114,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -11165,7 +11153,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -11204,7 +11192,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -11243,7 +11231,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -11282,7 +11270,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -11321,7 +11309,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -11360,7 +11348,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -11399,7 +11387,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -11438,7 +11426,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -11477,7 +11465,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -11516,7 +11504,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -11555,7 +11543,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -11594,7 +11582,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -11633,7 +11621,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -11672,7 +11660,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -11711,7 +11699,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -11750,7 +11738,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -11789,7 +11777,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -11828,7 +11816,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -11867,7 +11855,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -11906,7 +11894,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -11945,7 +11933,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -11984,7 +11972,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -12023,7 +12011,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -12062,7 +12050,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -12101,7 +12089,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -12140,7 +12128,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -12179,7 +12167,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -12218,7 +12206,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -12257,7 +12245,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -12296,7 +12284,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -12335,7 +12323,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -12374,7 +12362,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -12413,7 +12401,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -12452,7 +12440,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -12491,7 +12479,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -12530,7 +12518,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -12569,7 +12557,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -12608,7 +12596,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -12647,7 +12635,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -12686,7 +12674,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -12725,7 +12713,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -12764,7 +12752,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -12803,7 +12791,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -12842,7 +12830,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -12881,7 +12869,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -12920,7 +12908,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -12959,7 +12947,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -12998,7 +12986,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -13037,7 +13025,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -13076,7 +13064,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -13115,7 +13103,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -13154,7 +13142,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -13193,7 +13181,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -13232,7 +13220,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -13271,7 +13259,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -13310,7 +13298,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -13349,7 +13337,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -13388,7 +13376,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -13427,7 +13415,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -13466,7 +13454,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -13505,7 +13493,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -13544,7 +13532,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -13583,7 +13571,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -13622,7 +13610,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -13661,7 +13649,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -13700,7 +13688,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -13739,7 +13727,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -13778,7 +13766,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -13817,7 +13805,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -13856,7 +13844,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -13895,7 +13883,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -13934,7 +13922,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -13973,7 +13961,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -14012,7 +14000,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -14051,7 +14039,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -14090,7 +14078,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -14129,7 +14117,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -14168,7 +14156,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -14207,7 +14195,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -14246,7 +14234,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -14285,7 +14273,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -14324,7 +14312,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -14363,7 +14351,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -14402,7 +14390,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -14441,7 +14429,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -14480,7 +14468,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -14519,7 +14507,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -14558,7 +14546,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -14597,7 +14585,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -14636,7 +14624,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -14675,7 +14663,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -14714,7 +14702,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -14753,7 +14741,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -14792,7 +14780,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -14831,7 +14819,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -14870,7 +14858,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -14909,7 +14897,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -14948,7 +14936,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -14987,7 +14975,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -15026,7 +15014,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -15065,7 +15053,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -15104,7 +15092,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -15143,7 +15131,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -15182,7 +15170,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -15221,7 +15209,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -15260,7 +15248,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -15299,7 +15287,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -15338,7 +15326,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -15377,7 +15365,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -15416,7 +15404,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -15455,7 +15443,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -15494,7 +15482,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -15533,7 +15521,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -15572,7 +15560,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -15611,7 +15599,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -15650,7 +15638,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -15689,7 +15677,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -15728,7 +15716,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -15767,7 +15755,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -15806,7 +15794,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -15845,7 +15833,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -15884,7 +15872,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -15923,7 +15911,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -15962,7 +15950,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -16001,7 +15989,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -16040,7 +16028,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -16079,7 +16067,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -16118,7 +16106,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -16157,7 +16145,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -16196,7 +16184,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -16235,7 +16223,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -16274,7 +16262,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -16313,7 +16301,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -16352,7 +16340,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -16391,7 +16379,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -16430,7 +16418,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -16469,7 +16457,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -16508,7 +16496,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -16547,7 +16535,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -16586,7 +16574,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -16625,7 +16613,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -16664,7 +16652,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -16703,7 +16691,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -16742,7 +16730,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
@@ -16781,7 +16769,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -16820,7 +16808,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -16859,7 +16847,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -16898,7 +16886,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -16937,7 +16925,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -16974,7 +16962,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -17013,7 +17001,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -17052,7 +17040,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -17091,7 +17079,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -17130,7 +17118,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -17169,7 +17157,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -17208,7 +17196,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -17247,7 +17235,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -17286,7 +17274,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -17325,7 +17313,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -17364,7 +17352,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -17403,7 +17391,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -17442,7 +17430,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -17481,7 +17469,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
@@ -17520,7 +17508,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -17559,7 +17547,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -17598,7 +17586,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -17637,7 +17625,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -17676,7 +17664,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -17715,7 +17703,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
@@ -17754,7 +17742,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -17793,7 +17781,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -17832,7 +17820,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -17871,7 +17859,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -17910,7 +17898,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -17949,7 +17937,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -17988,7 +17976,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -18027,7 +18015,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -18066,7 +18054,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -18105,7 +18093,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
@@ -18144,7 +18132,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -18183,7 +18171,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -18222,7 +18210,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -18261,7 +18249,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -18300,7 +18288,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -18339,7 +18327,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
@@ -18378,7 +18366,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -18417,7 +18405,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -18456,7 +18444,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -18495,7 +18483,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -18534,7 +18522,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -18573,7 +18561,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -18612,7 +18600,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -18651,7 +18639,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -18690,7 +18678,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -18729,7 +18717,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
@@ -18768,7 +18756,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -18807,7 +18795,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -18846,7 +18834,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -18885,7 +18873,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -18924,7 +18912,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -18963,7 +18951,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -19002,7 +18990,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -19041,7 +19029,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
@@ -19080,7 +19068,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -19119,7 +19107,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -19158,7 +19146,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
@@ -19197,7 +19185,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -19236,7 +19224,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -19275,7 +19263,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -19314,7 +19302,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -19353,7 +19341,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -19392,7 +19380,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -19431,7 +19419,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -19470,7 +19458,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -19509,7 +19497,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -19548,7 +19536,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -19587,7 +19575,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -19626,7 +19614,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -19665,7 +19653,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -19704,7 +19692,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -19743,7 +19731,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>fixed_broadband</t>
+          <t>i154_FBB</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
